--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>75.42130765510164</v>
+        <v>12.25596249395402</v>
       </c>
       <c r="D2" t="n">
-        <v>3.416300793418374</v>
+        <v>0.5551488789304858</v>
       </c>
       <c r="E2" t="n">
-        <v>26.21976538515829</v>
+        <v>4.260711875088222</v>
       </c>
       <c r="F2" t="n">
-        <v>9.855062877737856</v>
+        <v>1.601447717632402</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>75.05517212031553</v>
+        <v>12.19646546955127</v>
       </c>
       <c r="D3" t="n">
-        <v>19.2129875055622</v>
+        <v>3.122110469653857</v>
       </c>
       <c r="E3" t="n">
-        <v>26.21976538515829</v>
+        <v>4.260711875088222</v>
       </c>
       <c r="F3" t="n">
-        <v>9.855062877737856</v>
+        <v>1.601447717632402</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.05235129884952</v>
+        <v>3.908507086063048</v>
       </c>
       <c r="D4" t="n">
-        <v>25.64401922245596</v>
+        <v>4.167153123649093</v>
       </c>
       <c r="E4" t="n">
-        <v>26.21976538515829</v>
+        <v>4.260711875088222</v>
       </c>
       <c r="F4" t="n">
-        <v>9.855062877737856</v>
+        <v>1.601447717632402</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.54829758502549</v>
+        <v>5.614098357566643</v>
       </c>
       <c r="D5" t="n">
-        <v>30.73199017604297</v>
+        <v>4.993948403606983</v>
       </c>
       <c r="E5" t="n">
-        <v>26.21976538515829</v>
+        <v>4.260711875088222</v>
       </c>
       <c r="F5" t="n">
-        <v>9.855062877737856</v>
+        <v>1.601447717632402</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>12.39543520775029</v>
+        <v>2.014258221259422</v>
       </c>
       <c r="D6" t="n">
-        <v>10.86385813571502</v>
+        <v>1.76537694705369</v>
       </c>
       <c r="E6" t="n">
-        <v>26.21976538515829</v>
+        <v>4.260711875088222</v>
       </c>
       <c r="F6" t="n">
-        <v>9.855062877737856</v>
+        <v>1.601447717632402</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
